--- a/Data/Bystrategi_Grenland/Trafikk/Reisemiddelfordeling_AlleReiser_2005_til_2024.xlsx
+++ b/Data/Bystrategi_Grenland/Trafikk/Reisemiddelfordeling_AlleReiser_2005_til_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telemarkfylke-my.sharepoint.com/personal/kjell-tore_haustveit_telemarkfylke_no/Documents/GitHub/Telemark/Data/Bystrategi_Grenland/Trafikk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{B17C5C38-29E4-4522-B170-C2AD8B6082BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F198C61-BE31-4267-B1EF-9C5E8D634DE6}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{B17C5C38-29E4-4522-B170-C2AD8B6082BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A45BE62C-5799-4713-924D-578C0A4069C2}"/>
   <bookViews>
-    <workbookView xWindow="10932" yWindow="624" windowWidth="21348" windowHeight="14916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="19116" windowHeight="15876" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
   <si>
     <t>Kommune</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>2020</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -531,30 +534,30 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
-        <v>2024</v>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C2">
         <v>17</v>
       </c>
       <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="H2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>61</v>
-      </c>
-      <c r="G2">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
       </c>
       <c r="I2">
         <f>C2+D2+E2+F2+G2+H2</f>
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -562,22 +565,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C3">
         <v>17</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -591,11 +594,11 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
+      <c r="B4" s="2">
+        <v>2023</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -604,17 +607,17 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <f>C4+D4+E4+F4+G4+H4</f>
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -622,28 +625,28 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I7" si="0">C5+D5+E5+F5+G5+H5</f>
+        <f>C5+D5+E5+F5+G5+H5</f>
         <v>100</v>
       </c>
     </row>
@@ -651,29 +654,29 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
-        <v>2009</v>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I6:I8" si="0">C6+D6+E6+F6+G6+H6</f>
         <v>100</v>
       </c>
     </row>
@@ -682,25 +685,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>57</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
         <v>3</v>
-      </c>
-      <c r="F7">
-        <v>59</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
@@ -709,19 +712,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2005</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>59</v>
@@ -730,10 +733,10 @@
         <v>13</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <f>C8+D8+E8+F8+G8+H8</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
@@ -742,29 +745,29 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <f t="shared" ref="I9:I15" si="1">C9+D9+E9+F9+G9+H9</f>
-        <v>101</v>
+        <f>C9+D9+E9+F9+G9+H9</f>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -772,28 +775,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>16</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>59</v>
       </c>
       <c r="G10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
+        <f>C10+D10+E10+F10+G10+H10</f>
         <v>100</v>
       </c>
     </row>
@@ -802,29 +805,29 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f t="shared" ref="I11:I18" si="1">C11+D11+E11+F11+G11+H11</f>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -832,25 +835,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
@@ -862,55 +865,55 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
         <v>17</v>
       </c>
-      <c r="C14">
-        <v>18</v>
-      </c>
       <c r="D14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
@@ -919,25 +922,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>18</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -952,29 +955,29 @@
         <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>16</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16">
         <v>12</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <f t="shared" ref="I16:I25" si="2">C16+D16+E16+F16+G16+H16</f>
-        <v>101</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -982,13 +985,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -997,13 +1000,13 @@
         <v>60</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17">
         <v>2</v>
       </c>
       <c r="I17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
@@ -1012,29 +1015,29 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>18</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G18">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <f t="shared" si="2"/>
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1042,55 +1045,55 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
         <v>16</v>
-      </c>
-      <c r="C19">
-        <v>19</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
-        <v>100</v>
+        <f t="shared" ref="I19:I30" si="2">C19+D19+E19+F19+G19+H19</f>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
         <v>2</v>
-      </c>
-      <c r="F20">
-        <v>69</v>
-      </c>
-      <c r="G20">
-        <v>13</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
       </c>
       <c r="I20">
         <f t="shared" si="2"/>
@@ -1099,28 +1102,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>56</v>
+      </c>
+      <c r="G21">
         <v>14</v>
       </c>
-      <c r="C21">
-        <v>11</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>73</v>
-      </c>
-      <c r="G21">
-        <v>10</v>
-      </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <f t="shared" si="2"/>
@@ -1129,58 +1132,58 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>19</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>58</v>
+      </c>
+      <c r="G22">
         <v>13</v>
-      </c>
-      <c r="C22">
-        <v>15</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>12</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
         <f t="shared" si="2"/>
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23">
         <v>14</v>
       </c>
-      <c r="C23">
-        <v>12</v>
-      </c>
       <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
       <c r="F23">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <f t="shared" si="2"/>
@@ -1189,28 +1192,28 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
         <v>2</v>
       </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
       <c r="F24">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G24">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <f t="shared" si="2"/>
@@ -1219,25 +1222,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1249,80 +1252,82 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>99</v>
+        <f t="shared" si="2"/>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -1331,64 +1336,67 @@
         <v>2</v>
       </c>
       <c r="I28">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30">
+        <v>16</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>61</v>
+      </c>
+      <c r="G30">
         <v>13</v>
-      </c>
-      <c r="C30">
-        <v>20</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>11</v>
-      </c>
-      <c r="F30">
-        <v>53</v>
-      </c>
-      <c r="G30">
-        <v>10</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
     </row>
@@ -1396,26 +1404,26 @@
       <c r="A31" t="s">
         <v>20</v>
       </c>
-      <c r="B31" t="s">
-        <v>14</v>
+      <c r="B31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -1426,19 +1434,19 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F32">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G32">
         <v>11</v>
@@ -1455,7 +1463,7 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <v>23</v>
@@ -1464,18 +1472,192 @@
         <v>5</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="F34">
+        <v>55</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <v>23</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>54</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>11</v>
+      </c>
+      <c r="F36">
+        <v>53</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37">
+        <v>22</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>54</v>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>22</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>52</v>
+      </c>
+      <c r="G38">
+        <v>11</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39">
+        <v>23</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>12</v>
+      </c>
+      <c r="F39">
+        <v>47</v>
+      </c>
+      <c r="G39">
+        <v>11</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
         <v>100</v>
       </c>
     </row>
@@ -1692,15 +1874,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aeab8c92-4fe2-4b74-b3c0-181f164372e7">
@@ -1709,6 +1882,15 @@
     <TaxCatchAll xmlns="28a90a7f-539e-46e9-b8b5-332cc23d9dd7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1731,14 +1913,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1915611-9028-4F81-BF7B-9404A03116EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D700F5C-A0F8-41B7-AD2F-910ACCC30B1B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1747,4 +1921,12 @@
     <ds:schemaRef ds:uri="28a90a7f-539e-46e9-b8b5-332cc23d9dd7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1915611-9028-4F81-BF7B-9404A03116EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>